--- a/mosip_master/xlsx/module_detail.xlsx
+++ b/mosip_master/xlsx/module_detail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8555"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="module_detail" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="40">
   <si>
     <t>id</t>
   </si>
@@ -74,7 +74,7 @@
     <t>t</t>
   </si>
   <si>
-    <t>System</t>
+    <t>admin</t>
   </si>
   <si>
     <t>f</t>
@@ -110,45 +110,6 @@
     <t>Web portal for Post ID generation services</t>
   </si>
   <si>
-    <t>पूर्व-पंजीकरण</t>
-  </si>
-  <si>
-    <t>पूर्व-पंजीकरण के लिए वेब पोर्टल</t>
-  </si>
-  <si>
-    <t>hin</t>
-  </si>
-  <si>
-    <t>पंजीकरण ग्राहक</t>
-  </si>
-  <si>
-    <t>पंजीकरण के लिए डेस्कटॉप एप्लिकेशन</t>
-  </si>
-  <si>
-    <t>पंजीकरण प्रोसेसर</t>
-  </si>
-  <si>
-    <t>पंजीकरण के बाद की प्रक्रिया के लिए आवेदन</t>
-  </si>
-  <si>
-    <t>आईडी प्रमाणीकरण</t>
-  </si>
-  <si>
-    <t>तृतीय पक्ष सेवा प्रदाता प्रमाणीकरण के लिए आवेदन</t>
-  </si>
-  <si>
-    <t>आईडी नियंत्रण</t>
-  </si>
-  <si>
-    <t>अनुप्रयोगों को कॉन्फ़िगर करने के लिए वेब पोर्टल</t>
-  </si>
-  <si>
-    <t>निवासी पोर्टल</t>
-  </si>
-  <si>
-    <t>पोस्ट आईडी जनरेशन सेवाओं के लिए वेब पोर्टल</t>
-  </si>
-  <si>
     <t>Preinscripción</t>
   </si>
   <si>
@@ -186,42 +147,6 @@
   </si>
   <si>
     <t>Portal web para servicios de generación de Post ID</t>
-  </si>
-  <si>
-    <t>Pré-inscription</t>
-  </si>
-  <si>
-    <t>Portail Web pour les pré-inscriptions</t>
-  </si>
-  <si>
-    <t>fra</t>
-  </si>
-  <si>
-    <t>Client d'inscription</t>
-  </si>
-  <si>
-    <t>Application de bureau pour les inscriptions</t>
-  </si>
-  <si>
-    <t>Processeur d'enregistrement</t>
-  </si>
-  <si>
-    <t>Demande de processus post-inscription</t>
-  </si>
-  <si>
-    <t>Authentification d'identité</t>
-  </si>
-  <si>
-    <t>Demande d'authentification d'un fournisseur de services tiers</t>
-  </si>
-  <si>
-    <t>Contrôle d'identité</t>
-  </si>
-  <si>
-    <t>Portail Web pour la configuration des applications</t>
-  </si>
-  <si>
-    <t>Portail résident</t>
   </si>
 </sst>
 </file>
@@ -1379,6 +1304,9 @@
   <sheetPr/>
   <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="18.6666666666667" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
@@ -1435,7 +1363,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="1">
-        <v>45526.6013811123</v>
+        <v>45667.2623750929</v>
       </c>
       <c r="J2" t="s">
         <v>16</v>
@@ -1461,7 +1389,7 @@
         <v>15</v>
       </c>
       <c r="G3" s="1">
-        <v>45526.6013811123</v>
+        <v>45667.2623750929</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -1487,7 +1415,7 @@
         <v>15</v>
       </c>
       <c r="G4" s="1">
-        <v>45526.6013811123</v>
+        <v>45667.2623750929</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
@@ -1513,7 +1441,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="1">
-        <v>45526.6013811123</v>
+        <v>45667.2623750929</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -1539,7 +1467,7 @@
         <v>15</v>
       </c>
       <c r="G6" s="1">
-        <v>45526.6013811123</v>
+        <v>45667.2623750929</v>
       </c>
       <c r="J6" t="s">
         <v>16</v>
@@ -1565,7 +1493,7 @@
         <v>15</v>
       </c>
       <c r="G7" s="1">
-        <v>45526.6013811123</v>
+        <v>45667.2623750929</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -1591,7 +1519,7 @@
         <v>15</v>
       </c>
       <c r="G8" s="1">
-        <v>45526.6013811123</v>
+        <v>45667.2623750929</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
@@ -1617,7 +1545,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="1">
-        <v>45526.6013811123</v>
+        <v>45667.2623750929</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
@@ -1643,7 +1571,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="1">
-        <v>45526.6013811123</v>
+        <v>45667.2623750929</v>
       </c>
       <c r="J10" t="s">
         <v>16</v>
@@ -1669,7 +1597,7 @@
         <v>15</v>
       </c>
       <c r="G11" s="1">
-        <v>45526.6013811123</v>
+        <v>45667.2623750929</v>
       </c>
       <c r="J11" t="s">
         <v>16</v>
@@ -1695,7 +1623,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="1">
-        <v>45526.6013811123</v>
+        <v>45667.2623750929</v>
       </c>
       <c r="J12" t="s">
         <v>16</v>
@@ -1721,323 +1649,47 @@
         <v>15</v>
       </c>
       <c r="G13" s="1">
-        <v>45526.6013811123</v>
+        <v>45667.2623750929</v>
       </c>
       <c r="J13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14">
-        <v>10001</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="1">
-        <v>45526.6013811123</v>
-      </c>
-      <c r="J14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15">
-        <v>10002</v>
-      </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="1">
-        <v>45526.6013811123</v>
-      </c>
-      <c r="J15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16">
-        <v>10003</v>
-      </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="1">
-        <v>45526.6013811123</v>
-      </c>
-      <c r="J16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17">
-        <v>10004</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="1">
-        <v>45526.6013811123</v>
-      </c>
-      <c r="J17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18">
-        <v>10005</v>
-      </c>
-      <c r="B18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="1">
-        <v>45526.6013811123</v>
-      </c>
-      <c r="J18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19">
-        <v>10006</v>
-      </c>
-      <c r="B19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="1">
-        <v>45526.6013811123</v>
-      </c>
-      <c r="J19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20">
-        <v>10001</v>
-      </c>
-      <c r="B20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="1">
-        <v>45526.6013811123</v>
-      </c>
-      <c r="J20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21">
-        <v>10002</v>
-      </c>
-      <c r="B21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="1">
-        <v>45526.6013811123</v>
-      </c>
-      <c r="J21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22">
-        <v>10003</v>
-      </c>
-      <c r="B22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" t="s">
-        <v>55</v>
-      </c>
-      <c r="E22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="1">
-        <v>45526.6013811123</v>
-      </c>
-      <c r="J22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23">
-        <v>10004</v>
-      </c>
-      <c r="B23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="1">
-        <v>45526.6013811123</v>
-      </c>
-      <c r="J23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24">
-        <v>10005</v>
-      </c>
-      <c r="B24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="1">
-        <v>45526.6013811123</v>
-      </c>
-      <c r="J24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25">
-        <v>10006</v>
-      </c>
-      <c r="B25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" t="s">
-        <v>55</v>
-      </c>
-      <c r="E25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="1">
-        <v>45526.6013811123</v>
-      </c>
-      <c r="J25" t="s">
-        <v>16</v>
-      </c>
+    <row r="14" spans="7:7">
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="7:7">
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="7:7">
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="7:7">
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="7:7">
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="7:7">
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="7:7">
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="7:7">
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="7:7">
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="7:7">
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="7:7">
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="7:7">
+      <c r="G25" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
